--- a/NWJSSP_ArturoMurgueytio_GRASP.xlsx
+++ b/NWJSSP_ArturoMurgueytio_GRASP.xlsx
@@ -13,8 +13,10 @@
     <sheet name="ft10r" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ft20" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tai_j100_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j10_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j10_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,6 +479,72 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n">
+        <v>125563</v>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>6649</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12832</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16666</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9241</v>
+      </c>
+      <c r="G2" t="n">
+        <v>837</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6319</v>
+      </c>
+      <c r="I2" t="n">
+        <v>14147</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3417</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -553,7 +621,7 @@
         <v>10676</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
@@ -619,7 +687,7 @@
         <v>12166</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>79</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2">
@@ -692,72 +760,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n">
-        <v>20855</v>
+        <v>19526</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>174</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>444</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C2" t="n">
+        <v>816</v>
+      </c>
+      <c r="D2" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>1503</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1068</v>
-      </c>
-      <c r="D2" t="n">
-        <v>952</v>
-      </c>
-      <c r="E2" t="n">
-        <v>110</v>
-      </c>
       <c r="F2" t="n">
-        <v>625</v>
+        <v>531</v>
       </c>
       <c r="G2" t="n">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="H2" t="n">
-        <v>229</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
-        <v>647</v>
+        <v>1289</v>
       </c>
       <c r="J2" t="n">
-        <v>1651</v>
+        <v>1566</v>
       </c>
       <c r="K2" t="n">
-        <v>423</v>
+        <v>206</v>
       </c>
       <c r="L2" t="n">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="M2" t="n">
-        <v>1203</v>
+        <v>976</v>
       </c>
       <c r="N2" t="n">
-        <v>1797</v>
+        <v>1712</v>
       </c>
       <c r="O2" t="n">
-        <v>614</v>
+        <v>661</v>
       </c>
       <c r="P2" t="n">
-        <v>854</v>
+        <v>802</v>
       </c>
       <c r="Q2" t="n">
-        <v>466</v>
+        <v>371</v>
       </c>
       <c r="R2" t="n">
-        <v>1650</v>
+        <v>1565</v>
       </c>
       <c r="S2" t="n">
-        <v>1372</v>
+        <v>1145</v>
       </c>
       <c r="T2" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -798,72 +866,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n">
-        <v>20652</v>
+        <v>20684</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>188</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="B2" t="n">
-        <v>975</v>
+        <v>877</v>
       </c>
       <c r="C2" t="n">
-        <v>693</v>
+        <v>595</v>
       </c>
       <c r="D2" t="n">
-        <v>577</v>
+        <v>479</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="G2" t="n">
-        <v>1883</v>
+        <v>1785</v>
       </c>
       <c r="H2" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
-        <v>1751</v>
+        <v>1653</v>
       </c>
       <c r="J2" t="n">
-        <v>1123</v>
+        <v>1025</v>
       </c>
       <c r="K2" t="n">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="L2" t="n">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="M2" t="n">
-        <v>1497</v>
+        <v>1399</v>
       </c>
       <c r="N2" t="n">
-        <v>1269</v>
+        <v>1171</v>
       </c>
       <c r="O2" t="n">
-        <v>1589</v>
+        <v>1491</v>
       </c>
       <c r="P2" t="n">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="Q2" t="n">
-        <v>609</v>
+        <v>1892</v>
       </c>
       <c r="R2" t="n">
-        <v>1122</v>
+        <v>1024</v>
       </c>
       <c r="S2" t="n">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="T2" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -872,6 +940,858 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n">
+        <v>6652646</v>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>464195</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B2" t="n">
+        <v>120280</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30685</v>
+      </c>
+      <c r="D2" t="n">
+        <v>90680</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38424</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12547</v>
+      </c>
+      <c r="G2" t="n">
+        <v>59471</v>
+      </c>
+      <c r="H2" t="n">
+        <v>67422</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6265</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>97775</v>
+      </c>
+      <c r="L2" t="n">
+        <v>35392</v>
+      </c>
+      <c r="M2" t="n">
+        <v>141022</v>
+      </c>
+      <c r="N2" t="n">
+        <v>61078</v>
+      </c>
+      <c r="O2" t="n">
+        <v>53632</v>
+      </c>
+      <c r="P2" t="n">
+        <v>22401</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>24458</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7878</v>
+      </c>
+      <c r="S2" t="n">
+        <v>142263</v>
+      </c>
+      <c r="T2" t="n">
+        <v>53271</v>
+      </c>
+      <c r="U2" t="n">
+        <v>83140</v>
+      </c>
+      <c r="V2" t="n">
+        <v>128538</v>
+      </c>
+      <c r="W2" t="n">
+        <v>34058</v>
+      </c>
+      <c r="X2" t="n">
+        <v>102635</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>80810</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16825</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>116027</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>98268</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>25803</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>18092</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>39714</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>72023</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>63177</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>101071</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75896</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>90162</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>29018</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>64110</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>128348</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65361</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>86402</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>87832</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>31205</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>107353</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>46735</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>126096</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>133333</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13173</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>80241</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>67319</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>114402</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>36721</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>128843</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>53872</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>138238</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>28418</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>20352</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>91692</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3635</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>93537</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>20734</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>75399</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>10449</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>94944</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>20480</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>43553</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>57269</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>966</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1263</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>36793</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5028</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>49736</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>48381</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>6621</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>70078</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>11640</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>56227</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>59721</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>120215</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>110920</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>121513</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>52149</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>116175</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>49424</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>107897</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>25715</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>110242</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>43760</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>33099</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>14533</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>82462</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>16312</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>72777</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>8036</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>77047</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>41274</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>104635</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>134942</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n">
+        <v>6624082</v>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>474104</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>22285</v>
+      </c>
+      <c r="B2" t="n">
+        <v>96700</v>
+      </c>
+      <c r="C2" t="n">
+        <v>115318</v>
+      </c>
+      <c r="D2" t="n">
+        <v>92092</v>
+      </c>
+      <c r="E2" t="n">
+        <v>74596</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5921</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35061</v>
+      </c>
+      <c r="H2" t="n">
+        <v>52005</v>
+      </c>
+      <c r="I2" t="n">
+        <v>64540</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4120</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81619</v>
+      </c>
+      <c r="L2" t="n">
+        <v>61427</v>
+      </c>
+      <c r="M2" t="n">
+        <v>56909</v>
+      </c>
+      <c r="N2" t="n">
+        <v>112485</v>
+      </c>
+      <c r="O2" t="n">
+        <v>138210</v>
+      </c>
+      <c r="P2" t="n">
+        <v>15168</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>99338</v>
+      </c>
+      <c r="R2" t="n">
+        <v>142057</v>
+      </c>
+      <c r="S2" t="n">
+        <v>132574</v>
+      </c>
+      <c r="T2" t="n">
+        <v>35310</v>
+      </c>
+      <c r="U2" t="n">
+        <v>83951</v>
+      </c>
+      <c r="V2" t="n">
+        <v>38601</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10189</v>
+      </c>
+      <c r="X2" t="n">
+        <v>26386</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>78834</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>133969</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>75223</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7470</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9501</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>30573</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>49320</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>57868</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>14795</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>80090</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>68593</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>137565</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>98650</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>114718</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>22478</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>66232</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>60128</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>38530</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>87481</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>117149</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>95691</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>99999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11576</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>69831</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>52576</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>73436</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>19392</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>81480</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>18149</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>106949</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>27616</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>511</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>54646</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>44583</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>123562</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>21544</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>4538</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>71562</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>19062</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>105723</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>7654</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>65296</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>39086</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>14506</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>22696</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>89749</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>26730</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>28549</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>128518</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>3096</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>45033</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>50158</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>31312</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>124361</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>107117</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>88778</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>122283</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>41717</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>101709</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>32410</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>104473</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>12500</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>111163</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>4888</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>34626</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>47569</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>24384</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>57098</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>2096</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>127811</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>121825</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>87870</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>117460</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -897,7 +1817,7 @@
         <v>138171</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>1083</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="2">
@@ -930,72 +1850,6 @@
       </c>
       <c r="J2" t="n">
         <v>7119</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>125563</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>6649</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D2" t="n">
-        <v>12832</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16666</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9241</v>
-      </c>
-      <c r="G2" t="n">
-        <v>837</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6319</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14147</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3417</v>
       </c>
     </row>
   </sheetData>
